--- a/docs/downloads/gsl-indexes/pdf_figure_headings.xlsx
+++ b/docs/downloads/gsl-indexes/pdf_figure_headings.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="About" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Index" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="pdf_figure_headings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Index'!$A$1:$H$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'pdf_figure_headings'!$A$1:$H$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,28 +29,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="002E4B70"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D7EFF8"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -76,15 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,89 +435,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>GSL PDF Extraction Export</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>PDF Extraction - Figure Headings</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>gsl_pdf_extraction_master.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Figure labels and captions detected from actual FIGURE X.X labels in the CPA PDF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Caveat</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Generated from PDF font/layout extraction; review before exam reliance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -548,4868 +449,4868 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Content/Text</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Current Heading</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Book Page</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PDF Page</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Source Line ID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.1 business environment</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>PREVIEW</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>P017-L011</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.2 2017</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>How Leaders in Data and Analytics Have Pulled Ahead</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>P020-L011</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.3</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.3 At high-performing</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>brought about by data and analytics in past 3 years1</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>% of respondents reporting a change in nature of industry competition brought about by data and analytics in past 3 years1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>P021-L001</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.4</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>1.2 THE STRATEGY PROCESS</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>P022-L001</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.5</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.5</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>and new service design, which are discussed in module 4.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>RESHAPING THE VALUE PROPOSITION</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>P030-L005</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.6</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.6 Non-price buyer value delivered</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>THE PRODUCTIVITY FRONTIER AND BEST PRACTICE</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>P032-L001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.7</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.7</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>INDUSTRY AND ORGANISATIONAL MATURITY</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>P034-L013</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.8</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.8</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Industry life cycle</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>P035-L001</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.9</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.9 Corporate head ofﬁce</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Functional Strategy</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>P037-L001</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.10</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.10</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>VISION, MISSION, VALUES AND GOALS</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>P040-L001</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.11</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.11 CUSTOMER</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>The Business Model Canvas</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>P044-L001</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.12</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.12 Shanghai</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>P048-L001</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.13</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.13 Team manager</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>The Behavioural Approach</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>P053-L008</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.14</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.14</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>STRATEGIC LEADERSHIP</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>P056-L001</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.15</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.15 Stace &amp; Dunphy</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>LEADERSHIP STYLES BASED ON THE INTENSITY OF CHANGE</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>P063-L021</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.16</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.16 Authoritarian</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>INDIVIDUAL DEVELOPMENTAL STAGE</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>LEADERSHIP STYLES BASED ON TEAM AND INDIVIDUAL DEVELOPMENTAL STAGE</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>P064-L029</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.17</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>FIGURE 1.17</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>LIFE CYCLE STAGE</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>LEADERSHIP STYLES BASED ON ORGANISATIONAL LIFE CYCLE STAGE</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>P065-L020</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.1</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.1 Global strategy and leadership</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>In module 1, we identified the stages of the process used in the rational approach to strategy. These stages</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>PREVIEW</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="G19" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>P085-L004</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.2</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.2</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Strategic analysis: Where are we now?</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>P086-L001</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.3</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.3 100</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Advanced Analytics in the Fisheries Industry</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="G21" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>P091-L006</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.4</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.4</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Advanced Analytics in the Fisheries Industry</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>P091-L041</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.5</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.5 processes</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>More Insightful Data Analysis</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="G23" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>P092-L024</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.6</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.6</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2.2 DEFINING THE INDUSTRY FOR ANALYSIS</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="G24" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>P095-L001</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.7</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.7 Supply</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>THE INDUSTRY VALUE CHAIN</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="G25" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>P096-L036</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.8</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.8</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fresh Food Industry Value Chain</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>P097-L007</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.9</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.9</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>QUESTION 2.3</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F27" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="G27" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>P098-L009</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.10</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.10</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>value chain</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="G28" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>P099-L001</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.11</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.11</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>The Global Pharmaceutical Value Chain</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="G29" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>P100-L013</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.12</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.12 Accessories: 12.0%</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>INDUSTRY SEGMENTATION</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="G30" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="G30" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>P102-L021</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.13</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.13 Supplementary</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Industry Segmentation</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="G31" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>P104-L018</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.14</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.14</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>mentioned in module 1, different styles of leadership and management are also often required at each of</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>THE INDUSTRY LIFE CYCLE</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="G32" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>P105-L010</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.15</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.15</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Disrupting the Industry Life Cycle</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="G33" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>P107-L016</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.16</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.16</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mature Organisations’ Response to Disruptive Technologies</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="G34" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>P108-L006</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.17</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.17 45.0%</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>The Accounting Services Industry Success Façade</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="G35" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>P109-L040</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.18</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.18 4.00%</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>The Accounting Services Industry Success Façade</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="G36" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>P110-L001</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.19</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.19 8.0</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>The Accounting Services Industry Success Façade</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="F37" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="G37" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>P110-L033</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.20</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.20 accountants*</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>1. Enabling Technologies</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="F38" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="G38" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>P111-L013</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.21</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.21 Price level</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>4. Economy</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="G39" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>P112-L023</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.22</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.22</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>FUTURE EXPECTATIONS</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="F40" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="G40" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>P115-L001</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.23</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.23 Ethical</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Factors Influencing Growth</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F41" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="G41" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>P116-L009</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.24</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.24 •Focus on experience.Technology has driven a shift away from traditional marketing towards the creation of</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Technological Factors</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="G42" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>P120-L004</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.25</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.25</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Market Segmentation</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>126</t>
         </is>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="F43" s="2" t="n">
         <v>141</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="G43" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>P141-L032</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.26</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.26 Logistics</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Market Segmentation in the Australian Domestic Airline Industry</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="G44" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>P143-L001</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.27</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>FIGURE 2.27 Luxury</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>IDENTIFYING STRATEGIC GROUPS</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="F45" s="2" t="n">
         <v>151</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="G45" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>P151-L019</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.1</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.1 Global strategy and leadership</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Module 2 focused on analysis of the external environment. This module focuses on the internal envi-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>PREVIEW</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="F46" s="2" t="n">
         <v>163</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="G46" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>P163-L006</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.2</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.2 External business drivers</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Strategic analysis: where are we now?</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="F47" s="2" t="n">
         <v>164</v>
       </c>
-      <c r="G47" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="G47" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>P164-L004</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.3</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.3</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>STEP 1: IDENTIFY STAKEHOLDERS AND THEIR NEEDS</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="F48" s="3" t="n">
+      <c r="F48" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="G48" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="G48" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>P165-L032</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.4</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.4</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>STAKEHOLDER GROUPS</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>STEP 3: ASSESS THE RELATIVE POWER OF STAKEHOLDER GROUPS</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="F49" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="G49" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="G49" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>P170-L005</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.5</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.5</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>A FRAMEWORK FOR PERFORMANCE ASSESSMENT</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="F50" s="2" t="n">
         <v>177</v>
       </c>
-      <c r="G50" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="G50" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>P177-L015</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.6</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.6 30 000</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>QUESTION 3.5</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>164</t>
         </is>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F51" s="2" t="n">
         <v>179</v>
       </c>
-      <c r="G51" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="G51" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>P179-L010</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.7</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.7</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>The Boston Consulting Group Product Matrix</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="F52" s="3" t="n">
+      <c r="F52" s="2" t="n">
         <v>181</v>
       </c>
-      <c r="G52" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="G52" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>P181-L027</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.8</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.8 90 000</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>QUESTION 3.8</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="F53" s="3" t="n">
+      <c r="F53" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="G53" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="G53" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>P183-L005</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.9</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.9 SOURCE OF COMPETITIVE</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>COMPETITIVE ADVANTAGE AND GENERIC STRATEGY</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>169</t>
         </is>
       </c>
-      <c r="F54" s="3" t="n">
+      <c r="F54" s="2" t="n">
         <v>184</v>
       </c>
-      <c r="G54" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="G54" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>P184-L001</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.10</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.10</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>THE BALANCED SCORECARD</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="F55" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="G55" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="G55" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>P195-L001</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.11</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.11 Financial</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>181</t>
         </is>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="F56" s="2" t="n">
         <v>196</v>
       </c>
-      <c r="G56" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="G56" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>P196-L001</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.12</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.12 2018</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>The Brave New World of Genomic Risk</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="F57" s="2" t="n">
         <v>199</v>
       </c>
-      <c r="G57" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="G57" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>P199-L001</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.13</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.13 Knowledge</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>An important enabler of learning organisations isknowledge management— how organisations</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F58" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="G58" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="G58" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>P201-L014</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.14</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.14 Levels of knowledge</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Data analytics</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>187</t>
         </is>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="F59" s="2" t="n">
         <v>202</v>
       </c>
-      <c r="G59" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="G59" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>P202-L001</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.15</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.15</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>IN STRATEGY</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>3.6 THE ROLE OF RESOURCES AND CAPABILITIES IN STRATEGY</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="F60" s="2" t="n">
         <v>203</v>
       </c>
-      <c r="G60" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="G60" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>P203-L001</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.16</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.16</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="F61" s="3" t="n">
+      <c r="F61" s="2" t="n">
         <v>203</v>
       </c>
-      <c r="G61" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="G61" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>P203-L026</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.17</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.17 Organisation capabilities as a hierarchy of integration: the case of oil and gas exploration</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>by Management</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Identifying Capabilities: the Creation of Organisational Capabilities by Management</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="F62" s="3" t="n">
+      <c r="F62" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="G62" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="G62" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>P205-L018</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.18</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.18 Business strategy</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>It is through the process of analysing the remote, industry and market environments (see module 2), and</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>GAP ANALYSIS</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>199</t>
         </is>
       </c>
-      <c r="F63" s="3" t="n">
+      <c r="F63" s="2" t="n">
         <v>214</v>
       </c>
-      <c r="G63" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="G63" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>P214-L025</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.19</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>FIGURE 3.19</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>The Commonwealth Bank of Australia (CBA) announced their financial and business results at</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="F64" s="3" t="n">
+      <c r="F64" s="2" t="n">
         <v>218</v>
       </c>
-      <c r="G64" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="G64" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>P218-L006</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.1</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.1 Global strategy and leadership</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>PREVIEW</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="F65" s="3" t="n">
+      <c r="F65" s="2" t="n">
         <v>223</v>
       </c>
-      <c r="G65" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
+      <c r="G65" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>P223-L006</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.2</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.2 Products</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>THE ANSOFF PRODUCT/MARKET MATRIX</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="F66" s="2" t="n">
         <v>231</v>
       </c>
-      <c r="G66" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="G66" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>P231-L038</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.3</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.3 Partnership</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>BRITA — Reducing Plastic Waste</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="F67" s="3" t="n">
+      <c r="F67" s="2" t="n">
         <v>246</v>
       </c>
-      <c r="G67" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="G67" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>P246-L001</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.4</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.4 Year 15</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="F68" s="3" t="n">
+      <c r="F68" s="2" t="n">
         <v>246</v>
       </c>
-      <c r="G68" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="G68" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>P246-L028</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.5</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.5</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>approval</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>232</t>
         </is>
       </c>
-      <c r="F69" s="3" t="n">
+      <c r="F69" s="2" t="n">
         <v>247</v>
       </c>
-      <c r="G69" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="G69" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>P247-L019</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.6</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.6 Customer</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>FOCUSING ON STRATEGICALLY IMPORTANT PROJECTS</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>234</t>
         </is>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="F70" s="2" t="n">
         <v>249</v>
       </c>
-      <c r="G70" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="G70" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>P249-L005</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.7</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.7 What Is Customer Jobs? What Is A Job to Be Done (JTBD)?</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>4.4 NEW SERVICE DEVELOPMENT</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="F71" s="3" t="n">
+      <c r="F71" s="2" t="n">
         <v>252</v>
       </c>
-      <c r="G71" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="G71" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>P252-L003</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.8</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.8</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Prototyping with 3D Printing</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>243</t>
         </is>
       </c>
-      <c r="F72" s="3" t="n">
+      <c r="F72" s="2" t="n">
         <v>258</v>
       </c>
-      <c r="G72" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="G72" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>P258-L001</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.9</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.9</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>SERVICE OFFERINGS</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>BLUE OCEAN STRATEGY — NEW PRODUCT AND SERVICE OFFERINGS</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>244</t>
         </is>
       </c>
-      <c r="F73" s="3" t="n">
+      <c r="F73" s="2" t="n">
         <v>259</v>
       </c>
-      <c r="G73" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="G73" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>P259-L028</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.10</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.10</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Blue Ocean Strategy</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="F74" s="3" t="n">
+      <c r="F74" s="2" t="n">
         <v>260</v>
       </c>
-      <c r="G74" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="G74" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>P260-L001</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.11</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.11 High</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Factors of Competition and the Strategy Canvas</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>246</t>
         </is>
       </c>
-      <c r="F75" s="3" t="n">
+      <c r="F75" s="2" t="n">
         <v>261</v>
       </c>
-      <c r="G75" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="G75" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>P261-L001</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.12</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.12 The six stages of buyer experience cycle</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Competing factors</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>246</t>
         </is>
       </c>
-      <c r="F76" s="3" t="n">
+      <c r="F76" s="2" t="n">
         <v>261</v>
       </c>
-      <c r="G76" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="G76" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>P261-L021</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.13</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.13</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>The Four Actions Framework</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="F77" s="2" t="n">
         <v>262</v>
       </c>
-      <c r="G77" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="G77" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>P262-L008</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.14</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.14 Eliminate</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>As is value curve</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>249</t>
         </is>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F78" s="2" t="n">
         <v>264</v>
       </c>
-      <c r="G78" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="G78" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>P264-L011</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.15</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.15</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Reduce</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>249</t>
         </is>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F79" s="2" t="n">
         <v>264</v>
       </c>
-      <c r="G79" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="G79" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>P264-L030</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.16</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.16 High</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Using the seven key factors of competition in the strategy canvas of the US Municipal Bus</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="F80" s="2" t="n">
         <v>265</v>
       </c>
-      <c r="G80" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="G80" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>P265-L034</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.17</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.17 VCRs</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Winning Standards Wars</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="F81" s="2" t="n">
         <v>269</v>
       </c>
-      <c r="G81" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="G81" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>P269-L003</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.18</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.18 Conﬁguration</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>DEVELOPMENT OF NEW GEOGRAPHIC MARKETS</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>257</t>
         </is>
       </c>
-      <c r="F82" s="3" t="n">
+      <c r="F82" s="2" t="n">
         <v>272</v>
       </c>
-      <c r="G82" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
+      <c r="G82" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>P272-L021</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.19</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.19</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Exporting</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="F83" s="3" t="n">
+      <c r="F83" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="G83" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="G83" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>P279-L001</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.20</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>FIGURE 4.20 Continually ask yourself where on the continuum your organisation falls, and what</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>As described in module 1, an organisation’s leaders are responsible for deciding and establishing an</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>4.8 LEADERSHIP</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>286</t>
         </is>
       </c>
-      <c r="F84" s="3" t="n">
+      <c r="F84" s="2" t="n">
         <v>301</v>
       </c>
-      <c r="G84" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="G84" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>P301-L035</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.1</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.1 Global strategy and leadership</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>suitable areas for growth and begin the strategy development through identifying options. Module 4</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>PREVIEW</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>296</t>
         </is>
       </c>
-      <c r="F85" s="3" t="n">
+      <c r="F85" s="2" t="n">
         <v>311</v>
       </c>
-      <c r="G85" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="G85" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>P311-L014</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.2</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.2 Develop</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>AND STRATEGY</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>5.1 ALIGNING VISION, MISSION, VALUES, GOALS AND STRATEGY</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>298</t>
         </is>
       </c>
-      <c r="F86" s="3" t="n">
+      <c r="F86" s="2" t="n">
         <v>313</v>
       </c>
-      <c r="G86" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="G86" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>P313-L001</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.3</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.3 Financial:To succeed ﬁnancially,</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>MOS M’s Goals</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>301</t>
         </is>
       </c>
-      <c r="F87" s="3" t="n">
+      <c r="F87" s="2" t="n">
         <v>316</v>
       </c>
-      <c r="G87" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="G87" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>P316-L011</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.4</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.4</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Employee Fi ndings</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>304</t>
         </is>
       </c>
-      <c r="F88" s="3" t="n">
+      <c r="F88" s="2" t="n">
         <v>319</v>
       </c>
-      <c r="G88" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="G88" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>P319-L001</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.5</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.5 Strategic drivers and factors for success</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>customer service representatives for some communications (Sawhney 2016). Consider the role</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="F89" s="3" t="n">
+      <c r="F89" s="2" t="n">
         <v>320</v>
       </c>
-      <c r="G89" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="G89" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>P320-L017</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.6</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.6</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>STRATEGIC DRIVERS</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>306</t>
         </is>
       </c>
-      <c r="F90" s="3" t="n">
+      <c r="F90" s="2" t="n">
         <v>321</v>
       </c>
-      <c r="G90" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="G90" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>P321-L021</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.7</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.7</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>307</t>
         </is>
       </c>
-      <c r="F91" s="3" t="n">
+      <c r="F91" s="2" t="n">
         <v>322</v>
       </c>
-      <c r="G91" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
+      <c r="G91" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>P322-L030</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.8</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.8</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Growth through new markets and communication</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>308</t>
         </is>
       </c>
-      <c r="F92" s="3" t="n">
+      <c r="F92" s="2" t="n">
         <v>323</v>
       </c>
-      <c r="G92" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="G92" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>P323-L008</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.9</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.9 Structure</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>ORGANISATION AND PEOPLE</t>
         </is>
       </c>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>309</t>
         </is>
       </c>
-      <c r="F93" s="3" t="n">
+      <c r="F93" s="2" t="n">
         <v>324</v>
       </c>
-      <c r="G93" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="G93" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>P324-L031</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.10</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.10 levers associated with a strategic option</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>THE INTERACTION OF DRIVERS AND LEVERS</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="F94" s="3" t="n">
+      <c r="F94" s="2" t="n">
         <v>327</v>
       </c>
-      <c r="G94" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="G94" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>P327-L001</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.11</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.11</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>(see module 6). These alignments and interdependencies are illustrated in figure 5.11. It is important to</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Zara — Str ategic Options</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>313</t>
         </is>
       </c>
-      <c r="F95" s="3" t="n">
+      <c r="F95" s="2" t="n">
         <v>328</v>
       </c>
-      <c r="G95" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
+      <c r="G95" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>P328-L004</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.12</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.12</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>VALUE/EFFORT ASSESSMENT</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="F96" s="3" t="n">
+      <c r="F96" s="2" t="n">
         <v>329</v>
       </c>
-      <c r="G96" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="G96" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>P329-L027</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.13</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.13 HOW DO DATA LAKES WORK?</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Data Lakes</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="F97" s="3" t="n">
+      <c r="F97" s="2" t="n">
         <v>335</v>
       </c>
-      <c r="G97" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
+      <c r="G97" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>P335-L020</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.14</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.14 Identify risk category and risk issue.</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>RISK MANAGEMENT FRAMEWORK</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>322</t>
         </is>
       </c>
-      <c r="F98" s="3" t="n">
+      <c r="F98" s="2" t="n">
         <v>337</v>
       </c>
-      <c r="G98" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="G98" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>P337-L007</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.15</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.15 Costs</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Nike Cost–Benefit Analysis</t>
         </is>
       </c>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="F99" s="3" t="n">
+      <c r="F99" s="2" t="n">
         <v>344</v>
       </c>
-      <c r="G99" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
+      <c r="G99" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>P344-L015</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.16</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.16 Strategic drivers</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>5.5 INTEGRATING STRATEGIC OPTIONS</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="F100" s="3" t="n">
+      <c r="F100" s="2" t="n">
         <v>346</v>
       </c>
-      <c r="G100" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
+      <c r="G100" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>P346-L011</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.17</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>FIGURE 5.17 VISION</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>MODULE 5</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>SETTING KEY PERFORMANCE METRICS</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>341</t>
         </is>
       </c>
-      <c r="F101" s="3" t="n">
+      <c r="F101" s="2" t="n">
         <v>356</v>
       </c>
-      <c r="G101" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
+      <c r="G101" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>P356-L001</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.1</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.1 Global strategy and leadership</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>This provided the foundation for developing strategic options in module 4. In module 5, we considered how</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>PREVIEW</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>362</t>
         </is>
       </c>
-      <c r="F102" s="3" t="n">
+      <c r="F102" s="2" t="n">
         <v>377</v>
       </c>
-      <c r="G102" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="G102" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>P377-L007</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.2</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.2</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>The7-S framework, developed by McKinsey &amp; Company in the 1980s, presents implementation as</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>365</t>
         </is>
       </c>
-      <c r="F103" s="3" t="n">
+      <c r="F103" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="G103" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
+      <c r="G103" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>P380-L017</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.3</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.3 Communication</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>KEY COMPONENTS OF CHANGE MANAGEMENT</t>
         </is>
       </c>
-      <c r="E104" s="3" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>381</t>
         </is>
       </c>
-      <c r="F104" s="3" t="n">
+      <c r="F104" s="2" t="n">
         <v>396</v>
       </c>
-      <c r="G104" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
+      <c r="G104" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>P396-L016</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.4</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.4 Organisational/</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>A STRUCTURED APPROACH TO MANAGING CHANGE</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>384</t>
         </is>
       </c>
-      <c r="F105" s="3" t="n">
+      <c r="F105" s="2" t="n">
         <v>399</v>
       </c>
-      <c r="G105" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
+      <c r="G105" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>P399-L010</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.5</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.5</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Kotter’s Eight-Step Process for Change</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>386</t>
         </is>
       </c>
-      <c r="F106" s="3" t="n">
+      <c r="F106" s="2" t="n">
         <v>401</v>
       </c>
-      <c r="G106" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
+      <c r="G106" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>P401-L010</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.6</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.6 2018</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>391</t>
         </is>
       </c>
-      <c r="F107" s="3" t="n">
+      <c r="F107" s="2" t="n">
         <v>406</v>
       </c>
-      <c r="G107" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
+      <c r="G107" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>P406-L001</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.7</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.7 Delivering today — performing against strategy</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Qantas BSC Metrics</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>397</t>
         </is>
       </c>
-      <c r="F108" s="3" t="n">
+      <c r="F108" s="2" t="n">
         <v>412</v>
       </c>
-      <c r="G108" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
+      <c r="G108" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>P412-L013</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.8</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.8 Financial</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Progress to date</t>
         </is>
       </c>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>398</t>
         </is>
       </c>
-      <c r="F109" s="3" t="n">
+      <c r="F109" s="2" t="n">
         <v>413</v>
       </c>
-      <c r="G109" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
+      <c r="G109" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>P413-L003</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.9</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>FIGURE 6.9</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Resistance</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>405</t>
         </is>
       </c>
-      <c r="F110" s="3" t="n">
+      <c r="F110" s="2" t="n">
         <v>420</v>
       </c>
-      <c r="G110" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="G110" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>P420-L024</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.1</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.1</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>a strategy intended to achieve the organisation’s vision and goals. Module 1 described the strategy</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>PREVIEW</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>419</t>
         </is>
       </c>
-      <c r="F111" s="3" t="n">
+      <c r="F111" s="2" t="n">
         <v>434</v>
       </c>
-      <c r="G111" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
+      <c r="G111" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>P434-L001</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.2</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.2</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Cloud Computing</t>
         </is>
       </c>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>422</t>
         </is>
       </c>
-      <c r="F112" s="3" t="n">
+      <c r="F112" s="2" t="n">
         <v>437</v>
       </c>
-      <c r="G112" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="G112" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>P437-L001</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.3</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.3 CUSTOMER</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>models and alternative ways to configure them. As described in module 1, abusiness model canvasis</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>BUSINESS MODEL CANVAS</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>428</t>
         </is>
       </c>
-      <c r="F113" s="3" t="n">
+      <c r="F113" s="2" t="n">
         <v>443</v>
       </c>
-      <c r="G113" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
+      <c r="G113" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>P443-L013</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.4</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.4 Customer</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>REVENUE STREAMS</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>429</t>
         </is>
       </c>
-      <c r="F114" s="3" t="n">
+      <c r="F114" s="2" t="n">
         <v>444</v>
       </c>
-      <c r="G114" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="G114" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>P444-L001</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.5</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.5 VALUE</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Business Model Canvas for an Online Retailer</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>430</t>
         </is>
       </c>
-      <c r="F115" s="3" t="n">
+      <c r="F115" s="2" t="n">
         <v>445</v>
       </c>
-      <c r="G115" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
+      <c r="G115" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>P445-L015</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.6</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.6 Disruptive</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>TRANSFORMATION AND DISRUPTION</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>434</t>
         </is>
       </c>
-      <c r="F116" s="3" t="n">
+      <c r="F116" s="2" t="n">
         <v>449</v>
       </c>
-      <c r="G116" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="G116" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>P449-L035</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.7</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.7 Outcomes</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>ALTERNATIVE APPROACHES TO STRATEGY</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>439</t>
         </is>
       </c>
-      <c r="F117" s="3" t="n">
+      <c r="F117" s="2" t="n">
         <v>454</v>
       </c>
-      <c r="G117" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
+      <c r="G117" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>P454-L032</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.8</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.8 Manage to</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Discovery-Driven Planning</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>441</t>
         </is>
       </c>
-      <c r="F118" s="3" t="n">
+      <c r="F118" s="2" t="n">
         <v>456</v>
       </c>
-      <c r="G118" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
+      <c r="G118" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>P456-L012</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.9</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.9</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Design thinkingwas introduced in module 4 as a product development tool. This approach can be extended</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Design Thinking</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="F119" s="3" t="n">
+      <c r="F119" s="2" t="n">
         <v>457</v>
       </c>
-      <c r="G119" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="G119" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>P457-L025</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.10</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.10 Strategic opportunities for new ventures can be categorised along two dimensions: attitude</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>THE STRATEGY COMPASS</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>446</t>
         </is>
       </c>
-      <c r="F120" s="3" t="n">
+      <c r="F120" s="2" t="n">
         <v>461</v>
       </c>
-      <c r="G120" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="G120" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>P461-L007</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.11</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.11 Low operating costs</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Ryanair — A Business Model for a Complex Mature Ecosystem</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>451</t>
         </is>
       </c>
-      <c r="F121" s="3" t="n">
+      <c r="F121" s="2" t="n">
         <v>466</v>
       </c>
-      <c r="G121" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
+      <c r="G121" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>P466-L016</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.12</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.12</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sustainability and Business Models</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>458</t>
         </is>
       </c>
-      <c r="F122" s="3" t="n">
+      <c r="F122" s="2" t="n">
         <v>473</v>
       </c>
-      <c r="G122" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="G122" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>P473-L035</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.13</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.13 Analysis</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>HYPERCOMPETITION: A STRATEGIC APPROACH</t>
         </is>
       </c>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>461</t>
         </is>
       </c>
-      <c r="F123" s="3" t="n">
+      <c r="F123" s="2" t="n">
         <v>476</v>
       </c>
-      <c r="G123" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
+      <c r="G123" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>P476-L019</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.14</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.14 Rather than organisation as machine, the agile organisation is a living organism</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>AGILE ORGANISATIONS</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>465</t>
         </is>
       </c>
-      <c r="F124" s="3" t="n">
+      <c r="F124" s="2" t="n">
         <v>480</v>
       </c>
-      <c r="G124" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="G124" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>P480-L028</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.15</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.15 There are five trademarks of agile organisations.</t>
         </is>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>AGILE ORGANISATIONS</t>
         </is>
       </c>
-      <c r="E125" s="3" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>466</t>
         </is>
       </c>
-      <c r="F125" s="3" t="n">
+      <c r="F125" s="2" t="n">
         <v>481</v>
       </c>
-      <c r="G125" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H125" s="3" t="inlineStr">
+      <c r="G125" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>P481-L005</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.16</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.16 Strategising</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>STRATEGIC INNOVATION</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>468</t>
         </is>
       </c>
-      <c r="F126" s="3" t="n">
+      <c r="F126" s="2" t="n">
         <v>483</v>
       </c>
-      <c r="G126" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H126" s="3" t="inlineStr">
+      <c r="G126" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>P483-L005</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.17</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.17</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>TECHNOLOGY-ENABLED BUSINESS MODELS</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>LEADERSHIP AND MANAGEMENT IMPLICATIONS OF TECHNOLOGY-ENABLED BUSINESS MODELS</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>474</t>
         </is>
       </c>
-      <c r="F127" s="3" t="n">
+      <c r="F127" s="2" t="n">
         <v>489</v>
       </c>
-      <c r="G127" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H127" s="3" t="inlineStr">
+      <c r="G127" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>P489-L001</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.18</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>FIGURE 7.18 IBM’s emerging business organisation (EBO) model</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>LEADERSHIP FOR ESTABLISHED BUSINESSES</t>
         </is>
       </c>
-      <c r="E128" s="3" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F128" s="3" t="n">
+      <c r="F128" s="2" t="n">
         <v>495</v>
       </c>
-      <c r="G128" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
+      <c r="G128" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>P495-L001</t>
         </is>
